--- a/macierz_wynikowa.xlsx
+++ b/macierz_wynikowa.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,251 +425,367 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:BE57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SBS number</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>SBS name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>age_of_first_flowering_d0</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Branching_d0</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d0</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d1</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d2</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d3</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d4</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d5</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d6</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d7</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d8</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d9</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d10</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Bud bank seasonality_d11</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Canopy height_d0</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Canopy height_d1</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Canopy height_d2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d1</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d2</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d3</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d4</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d5</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d6</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d7</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d8</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d9</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d10</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d11</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d12</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d13</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d14</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d15</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Dispersal type_d16</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Leaf dry matter content _d0</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Leaf mass_d0</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Leaf size_d0</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>age_of_first_flowering_v0_0</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Branching_0</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v0_0</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v0_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v0_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v1_0</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v1_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v1_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v2_0</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v2_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v2_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v3_0</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v3_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Bud bank seasonality_v3_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Canopy height_0</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Canopy height_1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Canopy height_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_0</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_4</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_7</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_8</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_9</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_10</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_11</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_12</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_13</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_14</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_15</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Dispersal type_v0_16</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Leaf dry matter content_0</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Leaf mass_0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Leaf size_0</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Plant growth form_v0_0</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Plant growth form_v0_1</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Plant growth form_v0_2</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Plant growth form_v0_3</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Plant life span_v0_0</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Plant life span_v0_1</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Plant life span_v0_2</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Plant life span_v0_3</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Seed bank_v0_0</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Seed bank_v0_1</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Seed bank_v0_2</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Seed mass_0</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Seed number_0</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Shoot growth form_v0_0</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Shoot growth form_v0_1</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Shoot growth form_v0_2</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Shoot growth form_v0_3</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Specific leaf area_0</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>166</v>
+        <v>3013</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equisetum arvense</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Achillea millefolium</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
-        <v>0.181547619047619</v>
+        <v>0.2235119047619047</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2121212121212122</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.125</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -666,25 +794,25 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -693,33 +821,85 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5510815592717311</v>
+        <v>0.3427315792477598</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.3377781339721855</v>
+        <v>0.0211703543000922</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.005071387040506492</v>
+        <v>0.0129530331416758</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.3870643079207112</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.4731922312399404</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.4438844396610342</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3013</v>
+        <v>41392</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Achillea millefolium</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
+          <t>Agrostis capillaris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>1</v>
       </c>
@@ -736,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -754,31 +934,31 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -787,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>1</v>
@@ -820,32 +1000,86 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3766908281490782</v>
+        <v>0.555519091376063</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0278850647858579</v>
+        <v>0.009783341857458223</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01295303314167582</v>
+        <v>0.01051962874432023</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.2918876126457607</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.3007410977837423</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.6203223528331558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5904</v>
+        <v>41907</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chamomilla suaveolens</t>
+          <t>Anthoxanthum odoratum</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -854,40 +1088,40 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.09226190476190477</v>
+        <v>0.08630952380952379</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06818181818181819</v>
+        <v>0.1363636363636363</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -917,13 +1151,13 @@
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>1</v>
@@ -935,28 +1169,80 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
         <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.2225900348153644</v>
+        <v>0.5969122766965356</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01429662845370175</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.01240390206085664</v>
+        <v>0.0020360523494435</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.6078856791354634</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.2652731602007112</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.6030255854310829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5994</v>
+        <v>16833</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chamomilla recutita</t>
+          <t>Arenaria serpyllifolia</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -978,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -996,22 +1282,22 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1279761904761905</v>
+        <v>0.08630952380952379</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.0227272727272727</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1020,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1035,10 +1321,10 @@
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1047,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1062,22 +1348,76 @@
         <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.13983220135837</v>
+        <v>0.4462288111409166</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01459226821218581</v>
+        <v>0.0004079169413656666</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.01540797209122036</v>
+        <v>0.2170144496845188</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.2977928953934427</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.4599109326638413</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.456868691671752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6638</v>
+        <v>14292</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Berteroa incana</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1087,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -1096,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1105,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1114,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1123,16 +1463,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1279761904761905</v>
+        <v>0.181547619047619</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1141,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1150,10 +1490,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>1</v>
@@ -1165,10 +1505,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1177,38 +1517,92 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
         <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.3772330346441413</v>
+        <v>0.5177929341932538</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.188229362221749</v>
+        <v>0.0061720910593036</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2039537437818981</v>
+        <v>0.0042396149622068</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.6185259667005056</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.5883080059964033</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.4221632447679918</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6658</v>
+        <v>12848</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hieracium pilosella</t>
+          <t>Capsella bursa-pastoris</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1217,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1235,22 +1629,22 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.06349206349206343</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03030303030303031</v>
+        <v>0.101010101010101</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.01515151515151513</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1262,13 +1656,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
@@ -1283,16 +1677,16 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1304,32 +1698,86 @@
         <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.353861080988528</v>
+        <v>0.2408681011357799</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.003917209825925688</v>
+        <v>0.05965412794072962</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.002454938949544544</v>
+        <v>0.05919848396752586</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.3493379814293474</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.5848424071434584</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.6057173940057305</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7298</v>
+        <v>14130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Leontodon autumnalis</t>
+          <t>Cardaminopsis arenosa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -1338,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1347,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1356,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1365,13 +1813,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.0773809523809523</v>
       </c>
       <c r="R8" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1392,13 +1840,13 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1407,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1422,33 +1870,89 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.3567147993835968</v>
+        <v>0.3905884367330632</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.1858604095099304</v>
+        <v>0.0042540707301176</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.1157051489114284</v>
+        <v>0.0044138294894157</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.367622346593506</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.4139521230116296</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.5771692951682297</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9565</v>
+        <v>37296</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Matricaria maritima</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Carex hirta</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1460,13 +1964,13 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1478,22 +1982,22 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.130952380952381</v>
+        <v>0.2559523809523809</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1502,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1511,60 +2015,112 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>1</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.498259231779008</v>
+        <v>0.6446121796701101</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04737018413004996</v>
+        <v>0.07336342599230523</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.006096970088507009</v>
+        <v>0.0551896924865947</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.8203246505604642</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.5067900963715517</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.4389916852114776</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10121</v>
+        <v>22963</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Senecio viscosus</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
+          <t>Centaurium erythraea</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>1</v>
       </c>
@@ -1605,34 +2161,34 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.072172619047619</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2424242424242425</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.03409090909090907</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1641,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1650,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -1665,29 +2221,83 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.228297471605502</v>
+        <v>0.5647984323573616</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.07238265268840993</v>
+        <v>0.01147992803397557</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.07817042444602365</v>
+        <v>0.00780089153046055</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.05900501219796384</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.6052274102249475</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.4724779895303691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10456</v>
+        <v>16782</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Senecio vulgaris</t>
+          <t>Cerastium arvense</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1699,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1717,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1726,16 +2336,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1071428571428572</v>
+        <v>0.05456349206349207</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.0707070707070707</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.05303030303030296</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1744,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1753,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>1</v>
@@ -1762,19 +2372,19 @@
         <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -1786,22 +2396,74 @@
         <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.08561155185206323</v>
+        <v>0.3792306375206894</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02857208345804154</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.02887783448543188</v>
+        <v>0.0009344201603726</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.4297520809291895</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.5028679310148206</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.4754602191352698</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11179</v>
+        <v>33202</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Senecio vernalis</t>
+          <t>Chaenorhinum minus</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1817,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1835,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1847,13 +2509,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.06646825396825394</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.0707070707070707</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1865,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1880,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1892,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -1904,29 +2566,83 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.07736430569031448</v>
+        <v>0.1703955253695565</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.05103901275972368</v>
+        <v>0.00316655247698204</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0469943148782221</v>
+        <v>0.002501372827702025</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.3026469444894409</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.5130770167333619</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.5531392938803046</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12105</v>
+        <v>5994</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Echium vulgare</t>
+          <t>Chamomilla recutita</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -1968,19 +2684,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3154761904761905</v>
+        <v>0.1279761904761904</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.2272727272727272</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1992,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>1</v>
@@ -2010,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -2022,28 +2738,82 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.2225900348153644</v>
+        <v>0.1303198067081406</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.2776345033640945</v>
+        <v>0.01053123926759016</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.145778151043349</v>
+        <v>0.01046579236384773</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.28288763692401</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.5795783849435032</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.7133656988299637</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12848</v>
+        <v>5904</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capsella bursa-pastoris</t>
+          <t>Chamomilla suaveolens</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2065,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2074,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2083,19 +2853,19 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1160714285714286</v>
+        <v>0.0922619047619047</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02272727272727272</v>
+        <v>0.06818181818181809</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -2113,10 +2883,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>1</v>
@@ -2125,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2137,7 +2907,7 @@
         <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2149,32 +2919,86 @@
         <v>1</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.3784601335540209</v>
+        <v>0.2016627665848601</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.1382198446114355</v>
+        <v>0.01317778326167655</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.09406292396149622</v>
+        <v>0.01117643258608435</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.3804313127765168</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.5570510772353092</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.5188326769380445</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13495</v>
+        <v>41702</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lepidium campestre</t>
+          <t>Corynephorus canescens</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -2183,46 +3007,46 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.0327380952380952</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.06818181818181809</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2234,13 +3058,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>1</v>
@@ -2249,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2258,34 +3082,86 @@
         <v>1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
         <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.4879858455567604</v>
+        <v>0.9357342617430512</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.02182608774596779</v>
+        <v>0.00103278017725395</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.02183603591963305</v>
+        <v>0.0007590929646617</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.4939792871217198</v>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.3429276499725308</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13947</v>
+        <v>16129</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lepidium ruderale</t>
+          <t>Dianthus deltoides</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2295,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -2304,16 +3180,16 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -2322,25 +3198,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1071428571428572</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2349,13 +3225,13 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2364,22 +3240,22 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2388,29 +3264,83 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.3139090234575652</v>
+        <v>0.5650362422236174</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.008183790416757982</v>
+        <v>0.00123545358038175</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.004360746818269914</v>
+        <v>0.00045222559596865</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.4522113363645336</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.3882828795405215</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.3955816029502184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14097</v>
+        <v>12105</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Erysimum cheiranthoides</t>
+          <t>Echium vulgare</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -2428,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2446,40 +3376,40 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3005952380952381</v>
+        <v>0.246031746031746</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
         <v>1</v>
@@ -2488,16 +3418,16 @@
         <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2512,77 +3442,105 @@
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.556475087038411</v>
+        <v>0.2225900348153644</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.08367776029953065</v>
+        <v>0.2776345033640945</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.06082434265779443</v>
+        <v>0.145778151043349</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.8294617558678842</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.4380408992382505</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.3605420644931778</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14130</v>
+        <v>166</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cardaminopsis arenosa</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
+          <t>Equisetum arvense</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.181547619047619</v>
       </c>
       <c r="R18" t="n">
-        <v>0.09090909090909093</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2954545454545454</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2633,26 +3591,62 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.4793105416357514</v>
+        <v>0.5008275783345699</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.007858965348818504</v>
+        <v>0.175479188117142</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.006173848439821694</v>
+        <v>0.0050713870405064</v>
+      </c>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.2468023111008932</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14292</v>
+        <v>14097</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Berteroa incana</t>
+          <t>Erysimum cheiranthoides</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -2670,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2688,22 +3682,22 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.181547619047619</v>
+        <v>0.1716269841269841</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.2323232323232323</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5227272727272727</v>
+        <v>0.2575757575757575</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2712,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2724,13 +3718,13 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2754,22 +3748,76 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.5201187146852349</v>
+        <v>0.4354679146928448</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.007760605331937172</v>
+        <v>0.04777639986213723</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.005265198010207378</v>
+        <v>0.03897753946206683</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.6549569205433087</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.4702338925836463</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.4967019391373937</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16129</v>
+        <v>20238</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dianthus deltoides</t>
+          <t>Euphorbia cyparissias</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2779,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -2794,10 +3842,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -2812,28 +3860,28 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.09226190476190473</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2424242424242425</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.2196969696969696</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2842,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2860,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -2872,35 +3920,83 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0.6734775412362308</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0.001239336212704796</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.0005491310808191744</v>
+        <v>1</v>
+      </c>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.7702240041298494</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.4114164133466584</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0.5148446296388807</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16755</v>
+        <v>40171</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stellaria media</t>
+          <t>Festuca ovina</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -2909,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2918,16 +4014,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2936,16 +4032,16 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1220238095238095</v>
+        <v>0.0788690476190476</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.103030303030303</v>
       </c>
       <c r="S21" t="n">
-        <v>0.06818181818181819</v>
+        <v>0.1477272727272727</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2954,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2963,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>1</v>
@@ -2978,16 +4074,16 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>1</v>
@@ -2996,38 +4092,90 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.09988014382740711</v>
+        <v>0.7437004166428857</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.00988906617954065</v>
+        <v>0.0022677727059746</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.02106079204082951</v>
+        <v>0.0005135021642224599</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.5386526892718629</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.3046125724378776</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0.3528269334209602</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16782</v>
+        <v>40103</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cerastium arvense</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
+          <t>Festuca rubra</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -3039,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -3057,16 +4205,16 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.2757936507936508</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06818181818181819</v>
+        <v>0.1439393939393939</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3075,7 +4223,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -3093,13 +4241,13 @@
         <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>1</v>
@@ -3108,39 +4256,95 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.3792306375206894</v>
+        <v>0.5793048341989612</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.0009344201603726632</v>
-      </c>
-      <c r="AM22" t="inlineStr"/>
+        <v>0.02394220004426785</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.0120162801214548</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.6584918547714161</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.352111064615929</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.4442116573421764</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16833</v>
+        <v>30633</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arenaria serpyllifolia</t>
+          <t>Fragaria vesca</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -3149,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3158,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3167,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3176,13 +4380,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.08630952380952382</v>
+        <v>0.05257936507936503</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.0606060606060606</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02272727272727272</v>
+        <v>0.06818181818181809</v>
       </c>
       <c r="T23" t="n">
         <v>0.1</v>
@@ -3203,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
         <v>1</v>
@@ -3212,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3221,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -3236,29 +4440,83 @@
         <v>1</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.5977683922150563</v>
+        <v>0.924604760002283</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.0007041220519154596</v>
+        <v>0.1304461972822399</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.6505265198010207</v>
+        <v>0.07699140771367655</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.5152365525682769</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.3940501204387848</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0.5052404755814652</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18178</v>
+        <v>30638</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sedum acre</t>
+          <t>Geum urbanum</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -3273,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3282,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3291,43 +4549,43 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.2063492063492063</v>
       </c>
       <c r="R24" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.2525252525252525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.02272727272727272</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="T24" t="n">
         <v>0.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
         <v>1</v>
@@ -3339,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>1</v>
@@ -3357,25 +4615,83 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
+        <v>0.6791849780263683</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.1492410524376233</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.1108275728406227</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.7580064021687778</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.4260707024823204</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0.6881513812138805</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19943</v>
+        <v>24650</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trifolium arvense</t>
+          <t>Glechoma hederacea</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -3390,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3399,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3408,28 +4724,28 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1636363636363636</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3438,16 +4754,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3456,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>1</v>
@@ -3465,41 +4781,95 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
         <v>1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.847554363335426</v>
+        <v>0.2739569659266023</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.01477480325611393</v>
+        <v>0.0203769510872455</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.00762323147490148</v>
+        <v>0.02816719426319525</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.6226809849099705</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.3463368582085358</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0.6563387935603329</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20238</v>
+        <v>6658</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Euphorbia cyparissias</t>
+          <t>Hieracium pilosella</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -3511,13 +4881,13 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -3529,25 +4899,25 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1220238095238095</v>
+        <v>0.0238095238095238</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2954545454545455</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3568,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
         <v>1</v>
@@ -3577,10 +4947,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -3594,24 +4964,82 @@
       <c r="AJ26" t="n">
         <v>1</v>
       </c>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
+      <c r="AK26" t="n">
+        <v>0.353861080988528</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.0039172098259256</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.0024549389495445</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.4355062088635253</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.3229844187610964</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0.4445950172767231</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20595</v>
+        <v>36112</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Medicago lupulina</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
+          <t>Juncus tenuis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -3626,10 +5054,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -3644,22 +5072,22 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2113095238095238</v>
+        <v>0.2306547619047619</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2787878787878788</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3674,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
@@ -3686,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -3695,44 +5123,98 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.4252040408652474</v>
+        <v>0.1421437132583756</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.02633866774130887</v>
+        <v>0.0139769583988374</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.02645519736417081</v>
+        <v>0.0086084372375476</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.1114813998195115</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.6592247309647229</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0.3260355170423905</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>21886</v>
+        <v>24182</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lotus corniculatus</t>
+          <t>Lamium album</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -3747,13 +5229,13 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -3765,25 +5247,25 @@
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0.1765873015873015</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0.1919191919191919</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="T28" t="n">
         <v>0.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3807,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -3825,35 +5307,89 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.5079618743222418</v>
+        <v>0.3024941498772901</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.00464500268311372</v>
+        <v>0.0417170255592536</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.004651463272821242</v>
+        <v>0.06332818657536013</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.7192995136532201</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.3072560287240846</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0.6656527359719837</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22096</v>
+        <v>7298</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trifolium pratense</t>
+          <t>Leontodon autumnalis</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -3868,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3886,22 +5422,22 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3005952380952381</v>
+        <v>0.02777777777777773</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.0222222222222222</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.053030303030303</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3910,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -3928,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -3943,38 +5479,92 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
         <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.5147537241025055</v>
+        <v>0.2619713486673135</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.03901941869682479</v>
+        <v>0.01911950752870679</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.03126816977840946</v>
+        <v>0.009368499257057903</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.6426846434583114</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.3955568918645177</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0.552455720322098</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22101</v>
+        <v>6638</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trifolium repens</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -3983,13 +5573,13 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4001,28 +5591,28 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1279761904761904</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -4055,43 +5645,99 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="n">
         <v>1</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.4150162661948519</v>
+        <v>0.2143313737800353</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.01863999565956918</v>
+        <v>0.06838094000335902</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.02354803281865754</v>
+        <v>0.07334668475569046</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.6903118887939969</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.3894079498704306</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.5492135769386871</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22963</v>
+        <v>13495</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Centaurium erythraea</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Lepidium campestre</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
@@ -4108,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4126,22 +5772,22 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.1622023809523809</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.1848484848484848</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -4150,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -4162,52 +5808,106 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
         <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="n">
         <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.7048684435819873</v>
+        <v>0.3981793276639461</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.02123911029941802</v>
+        <v>0.0165765267406574</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.008172362555720654</v>
+        <v>0.0131306931972349</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.7848249825640335</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.4592879100838231</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.5519533862559769</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>24182</v>
+        <v>13947</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lamium album</t>
+          <t>Lepidium ruderale</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4217,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -4226,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -4244,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -4253,16 +5953,16 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.06746031746031743</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.0606060606060606</v>
       </c>
       <c r="S32" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.1439393939393939</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -4274,16 +5974,16 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>1</v>
@@ -4292,16 +5992,16 @@
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -4313,22 +6013,76 @@
         <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.3624222361737344</v>
+        <v>0.2696763883339992</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.04516937875233014</v>
+        <v>0.00448985016198955</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.08139479294528071</v>
+        <v>0.00234188255055235</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.4399396746754042</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.5204531684735658</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0.4826447993541849</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>24350</v>
+        <v>43540</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Prunella vulgaris</t>
+          <t>Lolium perenne</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4338,7 +6092,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -4356,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -4374,13 +6128,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.09226190476190477</v>
+        <v>0.0625</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="S33" t="n">
-        <v>0.06818181818181819</v>
+        <v>0.06818181818181809</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
@@ -4398,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>1</v>
@@ -4416,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
         <v>1</v>
@@ -4434,22 +6188,76 @@
         <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.3365675475144113</v>
+        <v>0.4335154956908852</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.02746798956364812</v>
+        <v>0.0140555082493054</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0284902125460301</v>
+        <v>0.01266231668712445</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.774663189145181</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.677057569824415</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0.5375286037414255</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>24650</v>
+        <v>21886</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Glechoma hederacea</t>
+          <t>Lotus corniculatus</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4459,7 +6267,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -4468,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -4486,31 +6294,31 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.2435515873015873</v>
       </c>
       <c r="R34" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2676767676767677</v>
       </c>
       <c r="S34" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.04924242424242421</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -4528,10 +6336,10 @@
         <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4546,38 +6354,92 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ34" t="n">
         <v>1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.3196164602477027</v>
+        <v>0.3481536441983905</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.03329679638375857</v>
+        <v>0.004189382347651033</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.04770980037470121</v>
+        <v>0.003940823050584599</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0.725676039128752</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.433715359065588</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0.5199199889258869</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>27601</v>
+        <v>36245</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rumex acetosella</t>
+          <t>Luzula multiflora</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -4595,13 +6457,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4613,19 +6475,19 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.0972222222222222</v>
       </c>
       <c r="R35" t="n">
-        <v>0.09090909090909093</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4634,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -4649,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4658,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>1</v>
@@ -4670,33 +6532,85 @@
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.2197363164202956</v>
+        <v>0.4280577592603162</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.01806459013130148</v>
+        <v>0.0235620114808369</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.01250080754570709</v>
+        <v>0.0174106854447961</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0.5466229337986903</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0.4167892108717052</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0.5431578334774484</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>27740</v>
+        <v>9565</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Polygonum aviculare</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
+          <t>Matricaria maritima</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
         <v>1</v>
       </c>
@@ -4710,10 +6624,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4722,28 +6636,28 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1517857142857143</v>
+        <v>0.1309523809523809</v>
       </c>
       <c r="R36" t="n">
-        <v>1.181818181818182</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S36" t="n">
-        <v>0.06818181818181819</v>
+        <v>0.1363636363636363</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
@@ -4752,10 +6666,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -4776,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4785,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -4797,26 +6711,80 @@
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.4480337880257976</v>
+        <v>0.4603047771245933</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.01586948245427953</v>
+        <v>0.02781129477319685</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.01379288067704632</v>
+        <v>0.0048089346857032</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.5100429329218202</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.6392967353153934</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0.4659732235594041</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>27829</v>
+        <v>20595</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Plantago major</t>
+          <t>Medicago lupulina</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -4837,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -4855,19 +6823,19 @@
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="R37" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02272727272727272</v>
+        <v>0.1439393939393939</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4876,13 +6844,13 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
@@ -4906,7 +6874,7 @@
         <v>1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>1</v>
@@ -4918,13 +6886,67 @@
         <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.1227098909879573</v>
+        <v>0.3766908281490782</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
+        <v>0.0167589540541377</v>
       </c>
       <c r="AM37" t="n">
-        <v>1</v>
+        <v>0.01612937958955137</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0.7596692994833285</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0.3999444170402546</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0.5713770724599873</v>
       </c>
     </row>
     <row r="38">
@@ -4940,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -4979,13 +7001,13 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.1517857142857143</v>
+        <v>0.0840773809523809</v>
       </c>
       <c r="R38" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.1534090909090909</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
@@ -5039,22 +7061,76 @@
         <v>1</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.5507676502482735</v>
+        <v>0.2927237315221733</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.1216908410506357</v>
+        <v>0.08119369197638093</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.0887008204664384</v>
+        <v>0.08259577492086051</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0.7400321644902825</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.3585344656439821</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0.431456987819953</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>27974</v>
+        <v>27829</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Reseda lutea</t>
+          <t>Plantago major</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5079,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -5097,16 +7173,16 @@
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.3005952380952381</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="R39" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="S39" t="n">
-        <v>0.6363636363636362</v>
+        <v>-0.01136363636363635</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -5118,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5130,10 +7206,10 @@
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC39" t="n">
         <v>1</v>
@@ -5148,41 +7224,95 @@
         <v>1</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="n">
         <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.3424462074082529</v>
+        <v>0.1227098909879573</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.07466838554730568</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.04932489178887525</v>
+        <v>1</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0.4916788055950949</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0.514631953974882</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0.4965245558913764</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>29712</v>
+        <v>43060</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Potentilla anserina</t>
+          <t>Poa annua</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -5197,10 +7327,10 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -5215,19 +7345,19 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.181547619047619</v>
+        <v>0.0386904761904761</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.0606060606060606</v>
       </c>
       <c r="S40" t="n">
-        <v>0.2954545454545455</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
@@ -5236,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -5257,13 +7387,13 @@
         <v>1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF40" t="n">
         <v>1</v>
@@ -5272,31 +7402,85 @@
         <v>1</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ40" t="n">
         <v>1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.6535015124707494</v>
+        <v>0.5094315392957023</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.3343847133897795</v>
+        <v>0.0029220475251601</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.2803798695006137</v>
+        <v>0.004145401296379967</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0.4642842214594745</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0.4293504318745308</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0.6725332468913073</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>30633</v>
+        <v>42683</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fragaria vesca</t>
+          <t>Poa compressa</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5342,16 +7526,16 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.09226190476190477</v>
+        <v>0.2113095238095238</v>
       </c>
       <c r="R41" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S41" t="n">
-        <v>0.06818181818181819</v>
+        <v>0.2954545454545454</v>
       </c>
       <c r="T41" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5369,13 +7553,13 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC41" t="n">
         <v>1</v>
@@ -5384,10 +7568,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -5396,38 +7580,92 @@
         <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ41" t="n">
         <v>1</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.9474345071628332</v>
+        <v>0.6230618495900158</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.161350222279376</v>
+        <v>0.007006070098606934</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.1042056980425092</v>
+        <v>0.0051682925253569</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0.4535556073291336</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0.5828788496058794</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0.4515607594153687</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>30638</v>
+        <v>27740</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Geum urbanum</t>
+          <t>Polygonum aviculare</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -5436,49 +7674,49 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1294642857142857</v>
       </c>
       <c r="R42" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.7272727272727274</v>
       </c>
       <c r="S42" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.01136363636363635</v>
       </c>
       <c r="T42" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -5490,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA42" t="n">
         <v>1</v>
@@ -5502,7 +7740,7 @@
         <v>1</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5511,44 +7749,98 @@
         <v>1</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" t="n">
         <v>1</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.6791849780263683</v>
+        <v>0.4095085896923691</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.1492410524376233</v>
+        <v>0.0125590167640583</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.1108275728406228</v>
+        <v>0.0113540926416435</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0.7625236392481397</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0.4671693638522095</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0.5912574977151076</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>32792</v>
+        <v>29712</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Veronica chamaedrys</t>
+          <t>Potentilla anserina</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -5560,13 +7852,13 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -5578,31 +7870,31 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06646825396825394</v>
       </c>
       <c r="R43" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.08686868686868683</v>
       </c>
       <c r="S43" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.09848484848484847</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -5632,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -5644,26 +7936,80 @@
         <v>1</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.9388733519776268</v>
+        <v>0.4769205524798813</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.02278168664747132</v>
+        <v>0.1410024284399647</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.01253310937399057</v>
+        <v>0.2161099984925813</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0.6602298939708456</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0.2232712940835312</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0.516446895805507</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>33202</v>
+        <v>24350</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chaenorhinum minus</t>
+          <t>Prunella vulgaris</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
@@ -5675,13 +8021,13 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5693,25 +8039,25 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.08630952380952382</v>
+        <v>0.06150793650793646</v>
       </c>
       <c r="R44" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.08080808080808079</v>
       </c>
       <c r="S44" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.06060606060606053</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
@@ -5723,25 +8069,25 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -5759,32 +8105,86 @@
         <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.202614006049883</v>
+        <v>0.2819473774327949</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.006078649043266378</v>
+        <v>0.01560811297615798</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.003327088313198527</v>
+        <v>0.02149148308460923</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0.6246693967314804</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0.3435643131418964</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0.5961135096454916</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>35219</v>
+        <v>27974</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viola tricolor</t>
+          <t>Reseda lutea</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
@@ -5802,13 +8202,13 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -5820,31 +8220,31 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.2063492063492063</v>
       </c>
       <c r="R45" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.202020202020202</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.5227272727272726</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -5856,7 +8256,7 @@
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -5883,30 +8283,86 @@
         <v>1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.3424462074082529</v>
+        <v>0.2606396134162814</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.01777491228819265</v>
+        <v>0.05818146081811837</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.01566638671748821</v>
+        <v>0.03488597454615926</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0.613413601421387</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0.4170925388566398</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0.4338738747176588</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>36112</v>
+        <v>27601</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Juncus tenuis</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Rumex acetosella</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -5924,7 +8380,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -5942,16 +8398,16 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.0773809523809523</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3454545454545455</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
@@ -5963,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -5972,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA46" t="n">
         <v>1</v>
@@ -5987,10 +8443,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -5999,35 +8455,89 @@
         <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ46" t="n">
         <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.1421437132583757</v>
+        <v>0.1537697619998858</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.01397695839883742</v>
+        <v>0.009317713997732966</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.008608437237547645</v>
+        <v>0.0062880892391842</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0.5278970352288231</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0.4590856663430942</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0.5175520494682145</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>36245</v>
+        <v>18178</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Luzula multiflora</t>
+          <t>Sedum acre</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -6066,19 +8576,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.0218253968253968</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.0202020202020202</v>
       </c>
       <c r="S47" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.007575757575757566</v>
       </c>
       <c r="T47" t="n">
         <v>0.1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -6090,25 +8600,25 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF47" t="n">
         <v>1</v>
@@ -6126,22 +8636,72 @@
         <v>1</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.4280577592603162</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0.02356201148083691</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0.01741068544479617</v>
+        <v>0</v>
+      </c>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0.2179179570208979</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0.5476244632976576</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0.2297414871090304</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>37296</v>
+        <v>11179</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Carex hirta</t>
+          <t>Senecio vernalis</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6151,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -6160,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -6169,7 +8729,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -6178,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6187,16 +8747,16 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2559523809523809</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="R48" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S48" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2272727272727272</v>
       </c>
       <c r="T48" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -6214,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6229,13 +8789,13 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
@@ -6247,39 +8807,95 @@
         <v>1</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.7064094515153245</v>
+        <v>0.0773643056903144</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.1463498327245291</v>
+        <v>0.0510390127597236</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.08579365592092512</v>
+        <v>0.0469943148782221</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0.4198748897355186</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0.5061980644978966</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0.535971804100729</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>40103</v>
+        <v>10121</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Festuca rubra</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Senecio viscosus</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -6288,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -6297,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6306,13 +8922,13 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="R49" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="S49" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.2954545454545454</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
@@ -6333,16 +8949,16 @@
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>1</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6357,41 +8973,95 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
         <v>1</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.6420866388904742</v>
+        <v>0.1598082301238513</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.03695660221301972</v>
+        <v>0.06676170976082933</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.01201628012145487</v>
+        <v>0.05006783383939526</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0.5899272846111664</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0.5983733498580698</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0.4964613496045389</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>40171</v>
+        <v>10456</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Festuca ovina</t>
+          <t>Senecio vulgaris</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -6400,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -6409,16 +9079,16 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6427,16 +9097,16 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.1220238095238095</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="R50" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="S50" t="n">
         <v>0.1818181818181818</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -6454,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA50" t="n">
         <v>1</v>
@@ -6475,42 +9145,98 @@
         <v>1</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
         <v>1</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.9873865646937959</v>
+        <v>0.05707436790137545</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.005456934520369557</v>
+        <v>0.01706064628806455</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.0008912074423412366</v>
+        <v>0.0162478196265908</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0.4945786809470274</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0.5034695976235898</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0.6031544013566844</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>41392</v>
+        <v>16755</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Agrostis capillaris</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Stellaria media</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -6519,16 +9245,16 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>1</v>
@@ -6537,22 +9263,22 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.08730158730158727</v>
       </c>
       <c r="R51" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.06818181818181809</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
@@ -6564,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -6573,7 +9299,7 @@
         <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="n">
         <v>1</v>
@@ -6588,16 +9314,16 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
         <v>1</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI51" t="n">
         <v>1</v>
@@ -6606,35 +9332,85 @@
         <v>1</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.6211403458706696</v>
+        <v>0.05707436790137545</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.01676410339774154</v>
+        <v>0.008366734281801199</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.01414820078816461</v>
+        <v>0.0154402739195038</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0.5434639876714197</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0.3886812435887285</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0.7932232939940055</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>41702</v>
+        <v>44250</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Corynephorus canescens</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
+          <t>Taraxacum officinale</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -6646,7 +9422,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
@@ -6664,19 +9440,13 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0.03273809523809523</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.03030303030303031</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0.06818181818181819</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -6700,7 +9470,7 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6712,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -6724,35 +9494,47 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0.001662284285294527</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.0007590929646617998</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>41907</v>
+        <v>19943</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Anthoxanthum odoratum</t>
+          <t>Trifolium arvense</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -6761,43 +9543,43 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.08630952380952382</v>
+        <v>0.07539682539682536</v>
       </c>
       <c r="R53" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.07070707070707069</v>
       </c>
       <c r="S53" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -6806,13 +9588,13 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -6824,7 +9606,7 @@
         <v>1</v>
       </c>
       <c r="AC53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -6848,27 +9630,83 @@
         <v>1</v>
       </c>
       <c r="AK53" t="n">
-        <v>0.5969122766965356</v>
+        <v>0.6568189601050167</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.002036052349443593</v>
-      </c>
-      <c r="AM53" t="inlineStr"/>
+        <v>0.01150373310935968</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0.007203307707216167</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0.5195000452504213</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0.3635460776114138</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0.4387503042148657</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>42683</v>
+        <v>22096</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Poa compressa</t>
+          <t>Trifolium pratense</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -6907,16 +9745,16 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.2113095238095238</v>
+        <v>0.1567460317460317</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2525252525252525</v>
       </c>
       <c r="S54" t="n">
-        <v>0.2954545454545455</v>
+        <v>0.1439393939393939</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -6925,7 +9763,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
@@ -6934,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA54" t="n">
         <v>1</v>
@@ -6958,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI54" t="n">
         <v>1</v>
@@ -6967,26 +9805,80 @@
         <v>1</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.696307288396781</v>
+        <v>0.4399863021517036</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.009665946691015097</v>
+        <v>0.03181350491294017</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.006718780282964016</v>
+        <v>0.0227889398539957</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0.7398765093987604</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0.2301293132051241</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0.520349848433898</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>43060</v>
+        <v>22101</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Poa annua</t>
+          <t>Trifolium repens</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -6998,13 +9890,13 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -7016,25 +9908,25 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.03869047619047619</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="R55" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.0681818181818182</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
@@ -7070,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
         <v>1</v>
@@ -7088,22 +9980,76 @@
         <v>1</v>
       </c>
       <c r="AK55" t="n">
-        <v>0.6021345813595114</v>
+        <v>0.3485317618857371</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.005493441528171582</v>
+        <v>0.01132918636682553</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.005071387040506492</v>
+        <v>0.0217068286064991</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0.5953002914549079</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0.4183714306538416</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0.6225496396518425</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>43540</v>
+        <v>32792</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lolium perenne</t>
+          <t>Veronica chamaedrys</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -7113,7 +10059,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -7131,7 +10077,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -7149,16 +10095,16 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.0625</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="R56" t="n">
-        <v>0.09090909090909093</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="S56" t="n">
-        <v>0.06818181818181819</v>
+        <v>0.3712121212121213</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -7167,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -7185,55 +10131,113 @@
         <v>1</v>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
         <v>1</v>
       </c>
       <c r="AG56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
         <v>1</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.4984019176987615</v>
+        <v>0.6011738294998382</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.01896891696582128</v>
+        <v>0.01531315948075757</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.01550487757607081</v>
+        <v>0.01116028167194255</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0.4567717722662394</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0.2628909427112218</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0.6174537423409692</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>44250</v>
+        <v>35219</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Taraxacum officinale</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>Viola tricolor</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
       <c r="E57" t="n">
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -7245,13 +10249,13 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -7263,16 +10267,22 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.1369047619047619</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.1818181818181818</v>
+      </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -7287,16 +10297,16 @@
         <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -7305,7 +10315,7 @@
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -7314,14 +10324,74 @@
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0.3029507448205011</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.01422572139621607</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0.01390593707603845</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0.6163569231575858</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0.4589005564029968</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0.5740333145277813</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
